--- a/backend/tests/Fixtures/college_students_synthetic.xlsx
+++ b/backend/tests/Fixtures/college_students_synthetic.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="84">
   <si>
     <t>Name</t>
   </si>
@@ -244,9 +244,6 @@
   </si>
   <si>
     <t>24341D5702</t>
-  </si>
-  <si>
-    <t>VLSI &amp; ES</t>
   </si>
   <si>
     <t>Ravi Test</t>
@@ -1216,7 +1213,7 @@
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
         <v>19</v>
@@ -1239,19 +1236,19 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" t="s">
         <v>77</v>
-      </c>
-      <c r="B6" t="s">
-        <v>78</v>
       </c>
       <c r="D6" t="s">
         <v>23</v>
       </c>
       <c r="E6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" t="s">
         <v>79</v>
-      </c>
-      <c r="F6" t="s">
-        <v>80</v>
       </c>
       <c r="G6">
         <v>9876500017</v>
@@ -1271,10 +1268,10 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" t="s">
         <v>81</v>
-      </c>
-      <c r="B7" t="s">
-        <v>82</v>
       </c>
       <c r="C7">
         <v>2023</v>
@@ -1283,10 +1280,10 @@
         <v>29</v>
       </c>
       <c r="E7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F7" t="s">
         <v>83</v>
-      </c>
-      <c r="F7" t="s">
-        <v>84</v>
       </c>
       <c r="H7">
         <v>8.6</v>
